--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_17_0_TwoReleaseProduction_23Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_17_0_TwoReleaseProduction_23Aug2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA850CFE-B072-4CE7-AC3B-B50CEE561C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E0BB07-8085-491E-87D5-CEDB69BBC9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31965" yWindow="1605" windowWidth="37260" windowHeight="15960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Current Authority" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="Governance" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -5233,7 +5232,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5261,6 +5260,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5274,7 +5285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5288,11 +5299,17 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5614,6 +5631,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CurrentBacklogTable" displayName="CurrentBacklogTable" ref="A1:X165" totalsRowShown="0">
+  <autoFilter ref="A1:X165" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Worker 1"/>
+        <filter val="Worker 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task Id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Milestone Id"/>
@@ -5939,16 +5964,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2"/>
@@ -6128,15 +6153,16 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="9" width="58" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="12" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="16.375" customWidth="1"/>
     <col min="13" max="13" width="32" customWidth="1"/>
     <col min="14" max="14" width="30" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
@@ -6224,40 +6250,40 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="85.5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="7">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M2" s="2" t="s">
@@ -6298,40 +6324,40 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="99.75">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="7">
         <v>12</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -6372,40 +6398,40 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="85.5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="7">
         <v>12</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M4" s="2" t="s">
@@ -6893,7 +6919,7 @@
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -6921,9 +6947,9 @@
         <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1718</v>
-      </c>
-      <c r="L11" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M11" s="2"/>
@@ -6962,40 +6988,40 @@
       </c>
     </row>
     <row r="12" spans="1:24" ht="71.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="7">
         <v>10</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="K12" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>150</v>
       </c>
       <c r="M12" s="2" t="s">
@@ -7036,40 +7062,40 @@
       </c>
     </row>
     <row r="13" spans="1:24" ht="57">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="7">
         <v>10</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>150</v>
       </c>
       <c r="M13" s="2" t="s">
@@ -7110,40 +7136,40 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="71.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="5">
         <v>10</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L14" s="5" t="s">
         <v>150</v>
       </c>
       <c r="M14" s="2" t="s">
@@ -7257,41 +7283,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="85.5">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:24" ht="85.5" hidden="1">
+      <c r="A16" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="7">
         <v>8</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="K16" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M16" s="2" t="s">
@@ -7331,41 +7357,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="99.75">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:24" ht="99.75" hidden="1">
+      <c r="A17" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="7">
         <v>10</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="K17" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M17" s="2" t="s">
@@ -7405,41 +7431,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="71.25">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:24" ht="71.25" hidden="1">
+      <c r="A18" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="7">
         <v>6</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L18" s="2" t="s">
+      <c r="K18" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M18" s="2" t="s">
@@ -7553,41 +7579,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="57">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:24" ht="57" hidden="1">
+      <c r="A20" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="7">
         <v>5</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" s="2" t="s">
+      <c r="K20" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M20" s="2" t="s">
@@ -8515,7 +8541,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="156.75">
+    <row r="33" spans="1:24" ht="156.75" hidden="1">
       <c r="A33" s="2" t="s">
         <v>329</v>
       </c>
@@ -8589,7 +8615,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="242.25">
+    <row r="34" spans="1:24" ht="242.25" hidden="1">
       <c r="A34" s="2" t="s">
         <v>338</v>
       </c>
@@ -8735,7 +8761,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="85.5">
+    <row r="36" spans="1:24" ht="85.5" hidden="1">
       <c r="A36" s="2" t="s">
         <v>350</v>
       </c>
@@ -8950,40 +8976,40 @@
       </c>
     </row>
     <row r="39" spans="1:24" ht="71.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="7">
         <v>6</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L39" s="2" t="s">
+      <c r="K39" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M39" s="2" t="s">
@@ -10331,7 +10357,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="114">
+    <row r="58" spans="1:24" ht="114" hidden="1">
       <c r="A58" s="2" t="s">
         <v>550</v>
       </c>
@@ -10403,7 +10429,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="128.25">
+    <row r="59" spans="1:24" ht="128.25" hidden="1">
       <c r="A59" s="2" t="s">
         <v>567</v>
       </c>
@@ -10475,7 +10501,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="99.75">
+    <row r="60" spans="1:24" ht="99.75" hidden="1">
       <c r="A60" s="2" t="s">
         <v>573</v>
       </c>
@@ -10547,7 +10573,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="85.5">
+    <row r="61" spans="1:24" ht="85.5" hidden="1">
       <c r="A61" s="2" t="s">
         <v>579</v>
       </c>
@@ -10619,7 +10645,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="99.75">
+    <row r="62" spans="1:24" ht="99.75" hidden="1">
       <c r="A62" s="2" t="s">
         <v>584</v>
       </c>
@@ -10691,7 +10717,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="85.5">
+    <row r="63" spans="1:24" ht="85.5" hidden="1">
       <c r="A63" s="2" t="s">
         <v>591</v>
       </c>
@@ -10763,7 +10789,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="85.5">
+    <row r="64" spans="1:24" ht="85.5" hidden="1">
       <c r="A64" s="2" t="s">
         <v>597</v>
       </c>
@@ -10835,7 +10861,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="71.25">
+    <row r="65" spans="1:24" ht="71.25" hidden="1">
       <c r="A65" s="2" t="s">
         <v>603</v>
       </c>
@@ -10907,7 +10933,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="185.25">
+    <row r="66" spans="1:24" ht="185.25" hidden="1">
       <c r="A66" s="2" t="s">
         <v>608</v>
       </c>
@@ -10981,7 +11007,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="114">
+    <row r="67" spans="1:24" ht="114" hidden="1">
       <c r="A67" s="2" t="s">
         <v>614</v>
       </c>
@@ -11053,7 +11079,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="199.5">
+    <row r="68" spans="1:24" ht="199.5" hidden="1">
       <c r="A68" s="2" t="s">
         <v>620</v>
       </c>
@@ -11125,7 +11151,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="71.25">
+    <row r="69" spans="1:24" ht="71.25" hidden="1">
       <c r="A69" s="2" t="s">
         <v>626</v>
       </c>
@@ -11197,7 +11223,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="85.5">
+    <row r="70" spans="1:24" ht="85.5" hidden="1">
       <c r="A70" s="2" t="s">
         <v>632</v>
       </c>
@@ -11269,7 +11295,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="71" spans="1:24" ht="85.5">
+    <row r="71" spans="1:24" ht="85.5" hidden="1">
       <c r="A71" s="2" t="s">
         <v>638</v>
       </c>
@@ -11341,7 +11367,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="99.75">
+    <row r="72" spans="1:24" ht="99.75" hidden="1">
       <c r="A72" s="2" t="s">
         <v>643</v>
       </c>
@@ -11413,7 +11439,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="85.5">
+    <row r="73" spans="1:24" ht="85.5" hidden="1">
       <c r="A73" s="2" t="s">
         <v>648</v>
       </c>
@@ -11483,7 +11509,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="71.25">
+    <row r="74" spans="1:24" ht="71.25" hidden="1">
       <c r="A74" s="2" t="s">
         <v>653</v>
       </c>
@@ -11557,7 +11583,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="75" spans="1:24" ht="57">
+    <row r="75" spans="1:24" ht="57" hidden="1">
       <c r="A75" s="2" t="s">
         <v>664</v>
       </c>
@@ -11631,41 +11657,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="76" spans="1:24" ht="57">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:24" ht="57" hidden="1">
+      <c r="A76" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="I76" s="7" t="s">
         <v>677</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="7">
         <v>10</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L76" s="2" t="s">
+      <c r="K76" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L76" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M76" s="2" t="s">
@@ -11705,41 +11731,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="71.25">
-      <c r="A77" s="2" t="s">
+    <row r="77" spans="1:24" ht="71.25" hidden="1">
+      <c r="A77" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="I77" s="2" t="s">
+      <c r="I77" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="7">
         <v>8</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L77" s="2" t="s">
+      <c r="K77" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L77" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M77" s="2" t="s">
@@ -11779,41 +11805,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="114">
-      <c r="A78" s="2" t="s">
+    <row r="78" spans="1:24" ht="114" hidden="1">
+      <c r="A78" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="7" t="s">
         <v>692</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="I78" s="2" t="s">
+      <c r="I78" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="7">
         <v>12</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L78" s="2" t="s">
+      <c r="K78" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L78" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M78" s="2" t="s">
@@ -11853,41 +11879,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="71.25">
-      <c r="A79" s="2" t="s">
+    <row r="79" spans="1:24" ht="71.25" hidden="1">
+      <c r="A79" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="F79" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="I79" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="7">
         <v>8</v>
       </c>
-      <c r="K79" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L79" s="2" t="s">
+      <c r="K79" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L79" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M79" s="2" t="s">
@@ -11927,7 +11953,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="85.5">
+    <row r="80" spans="1:24" ht="85.5" hidden="1">
       <c r="A80" s="2" t="s">
         <v>710</v>
       </c>
@@ -11999,7 +12025,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="85.5">
+    <row r="81" spans="1:24" ht="85.5" hidden="1">
       <c r="A81" s="2" t="s">
         <v>720</v>
       </c>
@@ -12071,41 +12097,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="71.25">
-      <c r="A82" s="2" t="s">
+    <row r="82" spans="1:24" ht="71.25" hidden="1">
+      <c r="A82" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="I82" s="2" t="s">
+      <c r="I82" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="7">
         <v>8</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L82" s="2" t="s">
+      <c r="K82" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L82" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M82" s="2" t="s">
@@ -12145,41 +12171,41 @@
         <v>566</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="114">
-      <c r="A83" s="2" t="s">
+    <row r="83" spans="1:24" ht="114" hidden="1">
+      <c r="A83" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="7" t="s">
         <v>743</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="I83" s="2" t="s">
+      <c r="I83" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="7">
         <v>10</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L83" s="2" t="s">
+      <c r="K83" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L83" s="7" t="s">
         <v>191</v>
       </c>
       <c r="M83" s="2" t="s">
@@ -13651,7 +13677,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="71.25">
+    <row r="104" spans="1:24" ht="71.25" hidden="1">
       <c r="A104" s="2" t="s">
         <v>887</v>
       </c>
@@ -13721,7 +13747,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="85.5">
+    <row r="105" spans="1:24" ht="85.5" hidden="1">
       <c r="A105" s="2" t="s">
         <v>894</v>
       </c>
@@ -14941,7 +14967,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="85.5">
+    <row r="122" spans="1:24" ht="85.5" hidden="1">
       <c r="A122" s="2" t="s">
         <v>1000</v>
       </c>
@@ -15015,7 +15041,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="57">
+    <row r="123" spans="1:24" ht="57" hidden="1">
       <c r="A123" s="2" t="s">
         <v>1006</v>
       </c>
@@ -15089,7 +15115,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="124" spans="1:24" ht="71.25">
+    <row r="124" spans="1:24" ht="71.25" hidden="1">
       <c r="A124" s="2" t="s">
         <v>1015</v>
       </c>
@@ -15235,7 +15261,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="85.5">
+    <row r="126" spans="1:24" ht="85.5" hidden="1">
       <c r="A126" s="2" t="s">
         <v>1040</v>
       </c>
@@ -15309,7 +15335,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="71.25">
+    <row r="127" spans="1:24" ht="71.25" hidden="1">
       <c r="A127" s="2" t="s">
         <v>1053</v>
       </c>
@@ -15383,7 +15409,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="114">
+    <row r="128" spans="1:24" ht="114" hidden="1">
       <c r="A128" s="2" t="s">
         <v>1060</v>
       </c>
@@ -15457,7 +15483,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="129" spans="1:24" ht="71.25">
+    <row r="129" spans="1:24" ht="71.25" hidden="1">
       <c r="A129" s="2" t="s">
         <v>1066</v>
       </c>
@@ -15531,7 +15557,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="57">
+    <row r="130" spans="1:24" ht="57" hidden="1">
       <c r="A130" s="2" t="s">
         <v>1074</v>
       </c>
@@ -15605,7 +15631,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="71.25">
+    <row r="131" spans="1:24" ht="71.25" hidden="1">
       <c r="A131" s="2" t="s">
         <v>1079</v>
       </c>
@@ -15679,7 +15705,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="185.25">
+    <row r="132" spans="1:24" ht="185.25" hidden="1">
       <c r="A132" s="2" t="s">
         <v>1086</v>
       </c>
@@ -15753,7 +15779,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="171">
+    <row r="133" spans="1:24" ht="171" hidden="1">
       <c r="A133" s="2" t="s">
         <v>1093</v>
       </c>
@@ -15827,7 +15853,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="57">
+    <row r="134" spans="1:24" ht="57" hidden="1">
       <c r="A134" s="2" t="s">
         <v>1100</v>
       </c>
@@ -15899,7 +15925,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="114">
+    <row r="135" spans="1:24" ht="114" hidden="1">
       <c r="A135" s="2" t="s">
         <v>1106</v>
       </c>
@@ -15971,7 +15997,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="71.25">
+    <row r="136" spans="1:24" ht="71.25" hidden="1">
       <c r="A136" s="2" t="s">
         <v>1113</v>
       </c>
@@ -16045,7 +16071,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="71.25">
+    <row r="137" spans="1:24" ht="71.25" hidden="1">
       <c r="A137" s="2" t="s">
         <v>1121</v>
       </c>
@@ -16119,7 +16145,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="138" spans="1:24" ht="57">
+    <row r="138" spans="1:24" ht="57" hidden="1">
       <c r="A138" s="2" t="s">
         <v>1128</v>
       </c>
@@ -16193,7 +16219,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="139" spans="1:24" ht="71.25">
+    <row r="139" spans="1:24" ht="71.25" hidden="1">
       <c r="A139" s="2" t="s">
         <v>1135</v>
       </c>
@@ -16267,7 +16293,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="71.25">
+    <row r="140" spans="1:24" ht="71.25" hidden="1">
       <c r="A140" s="2" t="s">
         <v>631</v>
       </c>
@@ -16341,7 +16367,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="71.25">
+    <row r="141" spans="1:24" ht="71.25" hidden="1">
       <c r="A141" s="2" t="s">
         <v>1148</v>
       </c>
@@ -16415,7 +16441,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="142" spans="1:24" ht="57">
+    <row r="142" spans="1:24" ht="57" hidden="1">
       <c r="A142" s="2" t="s">
         <v>1154</v>
       </c>
@@ -16489,7 +16515,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="143" spans="1:24" ht="99.75">
+    <row r="143" spans="1:24" ht="99.75" hidden="1">
       <c r="A143" s="2" t="s">
         <v>1159</v>
       </c>
@@ -16561,7 +16587,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="144" spans="1:24" ht="199.5">
+    <row r="144" spans="1:24" ht="199.5" hidden="1">
       <c r="A144" s="2" t="s">
         <v>1166</v>
       </c>
@@ -16635,7 +16661,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="145" spans="1:24" ht="71.25">
+    <row r="145" spans="1:24" ht="71.25" hidden="1">
       <c r="A145" s="2" t="s">
         <v>1172</v>
       </c>
@@ -16705,7 +16731,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="146" spans="1:24" ht="57">
+    <row r="146" spans="1:24" ht="57" hidden="1">
       <c r="A146" s="2" t="s">
         <v>1178</v>
       </c>
@@ -16917,7 +16943,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="128.25">
+    <row r="149" spans="1:24" ht="128.25" hidden="1">
       <c r="A149" s="2" t="s">
         <v>1192</v>
       </c>
@@ -16991,7 +17017,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="150" spans="1:24" ht="156.75">
+    <row r="150" spans="1:24" ht="156.75" hidden="1">
       <c r="A150" s="2" t="s">
         <v>1200</v>
       </c>
@@ -17065,7 +17091,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="151" spans="1:24" ht="142.5">
+    <row r="151" spans="1:24" ht="142.5" hidden="1">
       <c r="A151" s="2" t="s">
         <v>1208</v>
       </c>
@@ -17139,7 +17165,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="85.5">
+    <row r="152" spans="1:24" ht="85.5" hidden="1">
       <c r="A152" s="2" t="s">
         <v>1214</v>
       </c>
@@ -17213,7 +17239,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="199.5">
+    <row r="153" spans="1:24" ht="199.5" hidden="1">
       <c r="A153" s="2" t="s">
         <v>596</v>
       </c>
@@ -17287,7 +17313,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="154" spans="1:24" ht="85.5">
+    <row r="154" spans="1:24" ht="85.5" hidden="1">
       <c r="A154" s="2" t="s">
         <v>1228</v>
       </c>
@@ -17361,7 +17387,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="71.25">
+    <row r="155" spans="1:24" ht="71.25" hidden="1">
       <c r="A155" s="2" t="s">
         <v>1133</v>
       </c>
@@ -17435,7 +17461,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="156" spans="1:24" ht="71.25">
+    <row r="156" spans="1:24" ht="71.25" hidden="1">
       <c r="A156" s="2" t="s">
         <v>1243</v>
       </c>
@@ -17509,7 +17535,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="99.75">
+    <row r="157" spans="1:24" ht="99.75" hidden="1">
       <c r="A157" s="2" t="s">
         <v>1250</v>
       </c>
@@ -17583,7 +17609,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="99.75">
+    <row r="158" spans="1:24" ht="99.75" hidden="1">
       <c r="A158" s="2" t="s">
         <v>1241</v>
       </c>
@@ -17657,7 +17683,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="114">
+    <row r="159" spans="1:24" ht="114" hidden="1">
       <c r="A159" s="2" t="s">
         <v>1263</v>
       </c>
@@ -17729,7 +17755,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="99.75">
+    <row r="160" spans="1:24" ht="99.75" hidden="1">
       <c r="A160" s="2" t="s">
         <v>1269</v>
       </c>
@@ -17803,7 +17829,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="85.5">
+    <row r="161" spans="1:24" ht="85.5" hidden="1">
       <c r="A161" s="2" t="s">
         <v>1277</v>
       </c>
@@ -17951,7 +17977,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="71.25">
+    <row r="163" spans="1:24" ht="71.25" hidden="1">
       <c r="A163" s="2" t="s">
         <v>1293</v>
       </c>
@@ -18214,18 +18240,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2"/>
@@ -18657,20 +18683,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1362</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
@@ -24877,18 +24903,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1370</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2"/>
@@ -29964,16 +29990,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1487</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2"/>
@@ -31746,14 +31772,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1680</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2"/>

--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_17_0_TwoReleaseProduction_23Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_17_0_TwoReleaseProduction_23Aug2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E0BB07-8085-491E-87D5-CEDB69BBC9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C02A981-D38C-4873-B9ED-AB6146B8D409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31965" yWindow="1605" windowWidth="37260" windowHeight="15960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Current Authority" sheetId="1" r:id="rId1"/>
@@ -5634,7 +5634,6 @@
   <autoFilter ref="A1:X165" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="11">
       <filters>
-        <filter val="Worker 1"/>
         <filter val="Worker 2"/>
       </filters>
     </filterColumn>
@@ -6249,7 +6248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="85.5">
+    <row r="2" spans="1:24" ht="85.5" hidden="1">
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
@@ -6323,7 +6322,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="99.75">
+    <row r="3" spans="1:24" ht="99.75" hidden="1">
       <c r="A3" s="7" t="s">
         <v>73</v>
       </c>
@@ -6397,7 +6396,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="85.5">
+    <row r="4" spans="1:24" ht="85.5" hidden="1">
       <c r="A4" s="7" t="s">
         <v>83</v>
       </c>
@@ -6471,41 +6470,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="85.5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:24" ht="85.5" hidden="1">
+      <c r="A5" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="7">
         <v>12</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M5" s="2" t="s">
@@ -6545,41 +6544,41 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="213.75">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:24" ht="213.75" hidden="1">
+      <c r="A6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="5">
         <v>12</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="K6" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M6" s="2" t="s">
@@ -6619,7 +6618,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="71.25">
+    <row r="7" spans="1:24" ht="71.25" hidden="1">
       <c r="A7" s="2" t="s">
         <v>106</v>
       </c>
@@ -6693,7 +6692,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="85.5">
+    <row r="8" spans="1:24" ht="85.5" hidden="1">
       <c r="A8" s="2" t="s">
         <v>112</v>
       </c>
@@ -6767,7 +6766,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="114">
+    <row r="9" spans="1:24" ht="114" hidden="1">
       <c r="A9" s="2" t="s">
         <v>120</v>
       </c>
@@ -6841,7 +6840,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="71.25">
+    <row r="10" spans="1:24" ht="71.25" hidden="1">
       <c r="A10" s="2" t="s">
         <v>127</v>
       </c>
@@ -6915,7 +6914,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="71.25">
+    <row r="11" spans="1:24" ht="71.25" hidden="1">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -7136,40 +7135,40 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="71.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="7">
         <v>10</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>1718</v>
-      </c>
-      <c r="L14" s="5" t="s">
+      <c r="K14" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>150</v>
       </c>
       <c r="M14" s="2" t="s">
@@ -7210,40 +7209,40 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="57">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="5">
         <v>8</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="K15" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>150</v>
       </c>
       <c r="M15" s="2" t="s">
@@ -7505,7 +7504,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="71.25">
+    <row r="19" spans="1:24" ht="71.25" hidden="1">
       <c r="A19" s="2" t="s">
         <v>218</v>
       </c>
@@ -7653,7 +7652,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="57">
+    <row r="21" spans="1:24" ht="57" hidden="1">
       <c r="A21" s="2" t="s">
         <v>238</v>
       </c>
@@ -7727,7 +7726,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="156.75">
+    <row r="22" spans="1:24" ht="156.75" hidden="1">
       <c r="A22" s="2" t="s">
         <v>248</v>
       </c>
@@ -7801,7 +7800,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="71.25">
+    <row r="23" spans="1:24" ht="71.25" hidden="1">
       <c r="A23" s="2" t="s">
         <v>260</v>
       </c>
@@ -7875,7 +7874,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="71.25">
+    <row r="24" spans="1:24" ht="71.25" hidden="1">
       <c r="A24" s="2" t="s">
         <v>266</v>
       </c>
@@ -8023,7 +8022,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="85.5">
+    <row r="26" spans="1:24" ht="85.5" hidden="1">
       <c r="A26" s="2" t="s">
         <v>281</v>
       </c>
@@ -8097,7 +8096,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="71.25">
+    <row r="27" spans="1:24" ht="71.25" hidden="1">
       <c r="A27" s="2" t="s">
         <v>289</v>
       </c>
@@ -8245,7 +8244,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="99.75">
+    <row r="29" spans="1:24" ht="99.75" hidden="1">
       <c r="A29" s="2" t="s">
         <v>301</v>
       </c>
@@ -8319,7 +8318,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="71.25">
+    <row r="30" spans="1:24" ht="71.25" hidden="1">
       <c r="A30" s="2" t="s">
         <v>309</v>
       </c>
@@ -8393,7 +8392,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="85.5">
+    <row r="31" spans="1:24" ht="85.5" hidden="1">
       <c r="A31" s="2" t="s">
         <v>315</v>
       </c>
@@ -8467,7 +8466,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="71.25">
+    <row r="32" spans="1:24" ht="71.25" hidden="1">
       <c r="A32" s="2" t="s">
         <v>323</v>
       </c>
@@ -8689,7 +8688,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="85.5">
+    <row r="35" spans="1:24" ht="85.5" hidden="1">
       <c r="A35" s="2" t="s">
         <v>345</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="71.25">
+    <row r="37" spans="1:24" ht="71.25" hidden="1">
       <c r="A37" s="2" t="s">
         <v>357</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="71.25">
+    <row r="38" spans="1:24" ht="71.25" hidden="1">
       <c r="A38" s="2" t="s">
         <v>361</v>
       </c>
@@ -8975,7 +8974,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="71.25">
+    <row r="39" spans="1:24" ht="71.25" hidden="1">
       <c r="A39" s="7" t="s">
         <v>368</v>
       </c>
@@ -9195,7 +9194,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="71.25">
+    <row r="42" spans="1:24" ht="71.25" hidden="1">
       <c r="A42" s="2" t="s">
         <v>402</v>
       </c>
@@ -9269,7 +9268,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="71.25">
+    <row r="43" spans="1:24" ht="71.25" hidden="1">
       <c r="A43" s="2" t="s">
         <v>412</v>
       </c>
@@ -9343,7 +9342,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="57">
+    <row r="44" spans="1:24" ht="57" hidden="1">
       <c r="A44" s="2" t="s">
         <v>420</v>
       </c>
@@ -9417,7 +9416,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="71.25">
+    <row r="45" spans="1:24" ht="71.25" hidden="1">
       <c r="A45" s="2" t="s">
         <v>429</v>
       </c>
@@ -9491,7 +9490,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="57">
+    <row r="46" spans="1:24" ht="57" hidden="1">
       <c r="A46" s="2" t="s">
         <v>439</v>
       </c>
@@ -9565,7 +9564,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="57">
+    <row r="47" spans="1:24" ht="57" hidden="1">
       <c r="A47" s="2" t="s">
         <v>449</v>
       </c>
@@ -12319,7 +12318,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="85.5">
+    <row r="85" spans="1:24" ht="85.5" hidden="1">
       <c r="A85" s="2" t="s">
         <v>765</v>
       </c>
@@ -12393,7 +12392,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="213.75">
+    <row r="86" spans="1:24" ht="213.75" hidden="1">
       <c r="A86" s="2" t="s">
         <v>776</v>
       </c>
@@ -12465,7 +12464,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="85.5">
+    <row r="87" spans="1:24" ht="85.5" hidden="1">
       <c r="A87" s="2" t="s">
         <v>781</v>
       </c>
@@ -12539,7 +12538,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="270.75">
+    <row r="88" spans="1:24" ht="270.75" hidden="1">
       <c r="A88" s="2" t="s">
         <v>787</v>
       </c>
@@ -12609,7 +12608,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="114">
+    <row r="89" spans="1:24" ht="114" hidden="1">
       <c r="A89" s="2" t="s">
         <v>791</v>
       </c>
@@ -12679,7 +12678,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="71.25">
+    <row r="90" spans="1:24" ht="71.25" hidden="1">
       <c r="A90" s="2" t="s">
         <v>796</v>
       </c>
@@ -12821,7 +12820,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="199.5">
+    <row r="92" spans="1:24" ht="199.5" hidden="1">
       <c r="A92" s="2" t="s">
         <v>806</v>
       </c>
@@ -12895,7 +12894,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="71.25">
+    <row r="93" spans="1:24" ht="71.25" hidden="1">
       <c r="A93" s="2" t="s">
         <v>813</v>
       </c>
@@ -12965,7 +12964,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="71.25">
+    <row r="94" spans="1:24" ht="71.25" hidden="1">
       <c r="A94" s="2" t="s">
         <v>818</v>
       </c>
@@ -13037,7 +13036,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="71.25">
+    <row r="95" spans="1:24" ht="71.25" hidden="1">
       <c r="A95" s="2" t="s">
         <v>824</v>
       </c>
@@ -13107,7 +13106,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="71.25">
+    <row r="96" spans="1:24" ht="71.25" hidden="1">
       <c r="A96" s="2" t="s">
         <v>828</v>
       </c>
@@ -13177,7 +13176,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="85.5">
+    <row r="97" spans="1:24" ht="85.5" hidden="1">
       <c r="A97" s="2" t="s">
         <v>180</v>
       </c>
@@ -13249,7 +13248,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="98" spans="1:24" ht="57">
+    <row r="98" spans="1:24" ht="57" hidden="1">
       <c r="A98" s="2" t="s">
         <v>843</v>
       </c>
@@ -13321,7 +13320,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="99" spans="1:24" ht="99.75">
+    <row r="99" spans="1:24" ht="99.75" hidden="1">
       <c r="A99" s="2" t="s">
         <v>852</v>
       </c>
@@ -13395,7 +13394,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="100" spans="1:24" ht="42.75">
+    <row r="100" spans="1:24" ht="42.75" hidden="1">
       <c r="A100" s="2" t="s">
         <v>865</v>
       </c>
@@ -13465,7 +13464,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="42.75">
+    <row r="101" spans="1:24" ht="42.75" hidden="1">
       <c r="A101" s="2" t="s">
         <v>873</v>
       </c>
@@ -13535,7 +13534,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="102" spans="1:24" ht="42.75">
+    <row r="102" spans="1:24" ht="42.75" hidden="1">
       <c r="A102" s="2" t="s">
         <v>425</v>
       </c>
@@ -13607,7 +13606,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="103" spans="1:24" ht="42.75">
+    <row r="103" spans="1:24" ht="42.75" hidden="1">
       <c r="A103" s="2" t="s">
         <v>882</v>
       </c>
@@ -13817,7 +13816,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="42.75">
+    <row r="106" spans="1:24" ht="42.75" hidden="1">
       <c r="A106" s="2" t="s">
         <v>899</v>
       </c>
@@ -13887,7 +13886,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="42.75">
+    <row r="107" spans="1:24" ht="42.75" hidden="1">
       <c r="A107" s="2" t="s">
         <v>904</v>
       </c>
@@ -13957,7 +13956,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="85.5">
+    <row r="108" spans="1:24" ht="85.5" hidden="1">
       <c r="A108" s="2" t="s">
         <v>908</v>
       </c>
@@ -14027,7 +14026,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="85.5">
+    <row r="109" spans="1:24" ht="85.5" hidden="1">
       <c r="A109" s="2" t="s">
         <v>915</v>
       </c>
@@ -14243,7 +14242,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="112" spans="1:24" ht="42.75">
+    <row r="112" spans="1:24" ht="42.75" hidden="1">
       <c r="A112" s="2" t="s">
         <v>933</v>
       </c>
@@ -14313,7 +14312,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="42.75">
+    <row r="113" spans="1:24" ht="42.75" hidden="1">
       <c r="A113" s="2" t="s">
         <v>937</v>
       </c>
@@ -14383,7 +14382,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="114" spans="1:24" ht="85.5">
+    <row r="114" spans="1:24" ht="85.5" hidden="1">
       <c r="A114" s="2" t="s">
         <v>925</v>
       </c>
@@ -16801,7 +16800,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="147" spans="1:24" ht="99.75">
+    <row r="147" spans="1:24" ht="99.75" hidden="1">
       <c r="A147" s="2" t="s">
         <v>760</v>
       </c>
@@ -16873,7 +16872,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="148" spans="1:24" ht="42.75">
+    <row r="148" spans="1:24" ht="42.75" hidden="1">
       <c r="A148" s="2" t="s">
         <v>1187</v>
       </c>
@@ -17903,7 +17902,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="71.25">
+    <row r="162" spans="1:24" ht="71.25" hidden="1">
       <c r="A162" s="2" t="s">
         <v>1287</v>
       </c>
@@ -18119,7 +18118,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="71.25">
+    <row r="165" spans="1:24" ht="71.25" hidden="1">
       <c r="A165" s="2" t="s">
         <v>1034</v>
       </c>
